--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00138_18940629.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -947,7 +947,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00138_18940629.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: only a gen Ã© ral</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+7684 CJK UNIFIED IDEOGRAPH-7684 | isolated marker/symbol line :: 的</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: he didn't care whether Her Majestyâ€™s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: L</t>
@@ -642,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -669,7 +673,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>923</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -692,19 +696,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œBut for the correction of the savage</t>
+          <t>L380: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wentworth School â€” Girls : Maggie</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: , 0</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+7684 CJK UNIFIED IDEOGRAPH-7684 | isolated marker/symbol line :: 的</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -723,7 +727,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -767,19 +775,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: called " orderâ€� Mr. Hardie refused to</t>
+          <t>L480: stray/suspicious non-ASCII glyph(s): U+7ECF CJK UNIFIED IDEOGRAPH-7ECF | isolated marker/symbol line :: 经</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Boysâ€™ Home- W. Hartzmark.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L275: isolated marker/symbol line :: , 0</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -798,7 +806,11 @@
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -814,12 +826,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -842,19 +854,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: gullible heirsâ€� spent $good</t>
+          <t>L552: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: lie, Florence Harvey ， Fannie L. Gunn,</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: architectureâ€”John M. Byrens.</t>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç»�</t>
+          <t>L380: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -869,7 +881,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -909,19 +925,15 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: rope, has ended with the conviction Ï� f</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Extra Advanced Course â€” Painting oil</t>
-        </is>
-      </c>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L665: isolated marker/symbol line :: 2</t>
+          <t>L480: stray/suspicious non-ASCII glyph(s): U+7ECF CJK UNIFIED IDEOGRAPH-7ECF | isolated marker/symbol line :: 经</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -976,24 +988,20 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: These â€œfakes " are so common and so</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mechanical Art Courseâ€”Industrial de-</t>
-        </is>
-      </c>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L666: isolated marker/symbol line :: 2</t>
+          <t>L665: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L665: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1041,21 +1049,13 @@
           <t>L349: suspicious token(s): 10c (letter/digit mix), 25o (letter/digit mix) :: 200 doz. Ladies' Vests 10c, worth 25o.</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Advanced Art Course â€” Shading from,</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L666: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1101,24 +1101,16 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç»�</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L319: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " It canâ€™t be true," she said, "that</t>
-        </is>
-      </c>
+          <t>L351: suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladies’ Cotton Drawers 15c, worth 506.</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L727: isolated marker/symbol line :: 0</t>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1145,12 +1137,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1167,21 +1159,13 @@
           <t>L353: punctuation artifact: repeated periods | suspicious token(s): 5c (letter/digit mix) :: Children's Vests, all sizes, 5c..</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L751: isolated marker/symbol line :: 3</t>
+          <t>L727: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1213,7 +1197,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1230,21 +1214,13 @@
           <t>L355: suspicious token(s): 10c (letter/digit mix), 25c (letter/digit mix) :: Children's Vests, fine, 10c, worth 25c.</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L766: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " It can't be trueâ€� she said," that</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Pursesâ€”a large purchase of fine new goods.</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L782: isolated marker/symbol line :: 7</t>
+          <t>L751: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1271,7 +1247,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1293,21 +1269,13 @@
           <t>L357: suspicious token(s): 15c (letter/digit mix), 35c (letter/digit mix) :: Lamp Shade Laces 15c, worth 35c.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . old question of taxationâ€”whether</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L783: isolated marker/symbol line :: A</t>
+          <t>L782: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1357,16 +1325,12 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fosterâ€™s latest tariff bill, and it will be</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L783: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1398,7 +1362,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1416,16 +1380,12 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L792: isolated marker/symbol line :: w</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1475,16 +1435,12 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rontoâ€™s asphalt pavement, which he</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L800: isolated marker/symbol line :: N</t>
+          <t>L792: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1534,16 +1490,12 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ done in the first instance, repairs will</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 1</t>
+          <t>L800: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1593,16 +1545,12 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Poem read at Miss Willardâ€™s welcome</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L820: isolated marker/symbol line :: N</t>
+          <t>L809: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1631,7 +1579,7 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>L512: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 Â½ c.</t>
+          <t>L512: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 ½ c.</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -1640,16 +1588,12 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Thereâ€™s but one sphere for man and</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L831: isolated marker/symbol line :: G</t>
+          <t>L820: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1687,16 +1631,12 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: To Hades heâ€™ll be soon remanded.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L841: isolated marker/symbol line :: S</t>
+          <t>L831: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1725,7 +1665,7 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>L561: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19 Â½ C</t>
+          <t>L561: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19 ½ C</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -1734,14 +1674,14 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L840: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And thatâ€™s the case with all his minions:</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>L841: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
           <t>L1032: symbol-only separator/garbage line :: 100,</t>
@@ -1777,11 +1717,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: From dirty politics": theyâ€™ve wielded</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
@@ -1820,11 +1756,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: When, in a hencoopâ€™s safe dominions,</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
@@ -1863,11 +1795,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L852: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ve not observed the uncaged bird</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
@@ -1906,11 +1834,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: In government, and-thereâ€™s the rub!</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
@@ -1949,11 +1873,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L867: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The very halls of state theyâ€™ll scrub,</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
@@ -1992,11 +1912,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And when theyâ€™ve tried it, fact discloses</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
@@ -2035,11 +1951,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: That even election dayâ€™s serene.</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr"/>
@@ -2078,11 +1990,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At freedomâ€™s fount, till, newly fledged,</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr"/>
@@ -2121,11 +2029,7 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: And yetâ€”this woman cannot vote !</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
@@ -2164,11 +2068,7 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Works. It is stipulated that the stone</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr"/>
@@ -2198,7 +2098,7 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>L669: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12 Â½.</t>
+          <t>L669: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12 ½.</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
@@ -2207,11 +2107,7 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Get Mowatâ€™s majority down as fine as</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
@@ -2250,11 +2146,7 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L1061: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: for the Governorship. If Mr. Singerlyâ€™s</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
@@ -2293,11 +2185,7 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Whatâ€™s this we see? Sir John Thomp-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
@@ -2332,11 +2220,7 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L1108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ning shoes at Kingsleyâ€™s, Nos. 26 and 28</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
@@ -2371,11 +2255,7 @@
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L1154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are you savinâ€™ up for the Fourth of</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
@@ -2410,11 +2290,7 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ll have 25 cents."</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
@@ -2430,37 +2306,6 @@
       <c r="X36" s="1" t="inlineStr"/>
       <c r="Y36" s="1" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L1208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ up the system.</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
